--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/GEORGIA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/GEORGIA_2016.xlsx
@@ -427,7 +427,7 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="5">
@@ -2119,7 +2119,7 @@
         <v>25</v>
       </c>
       <c r="D98">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="99">
@@ -2191,7 +2191,7 @@
         <v>25</v>
       </c>
       <c r="D102">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="103">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C132">
@@ -3253,7 +3253,7 @@
         <v>253</v>
       </c>
       <c r="D161">
-        <v>0.009740134744947065</v>
+        <v>0.009740134744947063</v>
       </c>
     </row>
     <row r="162">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C178">
@@ -4405,7 +4405,7 @@
         <v>25</v>
       </c>
       <c r="D225">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="226">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C318">
@@ -10057,7 +10057,7 @@
         <v>25</v>
       </c>
       <c r="D539">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="540">
@@ -12199,7 +12199,7 @@
         <v>25</v>
       </c>
       <c r="D658">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="659">
@@ -12523,7 +12523,7 @@
         <v>25</v>
       </c>
       <c r="D676">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="677">
@@ -12721,7 +12721,7 @@
         <v>25</v>
       </c>
       <c r="D687">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="688">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C758">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C759">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C866">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C867">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C907">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C908">
@@ -17545,7 +17545,7 @@
         <v>25</v>
       </c>
       <c r="D955">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="956">
@@ -18841,7 +18841,7 @@
         <v>25</v>
       </c>
       <c r="D1027">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="1028">
@@ -22117,7 +22117,7 @@
         <v>25</v>
       </c>
       <c r="D1209">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="1210">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1332">
@@ -25393,7 +25393,7 @@
         <v>25</v>
       </c>
       <c r="D1391">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="1392">
@@ -25699,7 +25699,7 @@
         <v>25</v>
       </c>
       <c r="D1408">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="1409">
@@ -27769,7 +27769,7 @@
         <v>25</v>
       </c>
       <c r="D1523">
-        <v>0.0009624639076034649</v>
+        <v>0.0009624639076034648</v>
       </c>
     </row>
     <row r="1524">
